--- a/IMS/src/main/webapp/excelTemplate/blueprintDetail.xlsx
+++ b/IMS/src/main/webapp/excelTemplate/blueprintDetail.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\h1\excelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\innost\Desktop\IMS수정txt\excelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16950" windowHeight="12060" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,10 +65,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 작성일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 작성자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -81,10 +77,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>변경관리 상세</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>변경관리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -234,6 +226,14 @@
   </si>
   <si>
     <t>첨부파일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 등록일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경정보 상세</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -817,6 +817,51 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -824,61 +869,16 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1599,16 +1599,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+      <c r="A1" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
     </row>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="3" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2"/>
     </row>
@@ -1644,132 +1644,132 @@
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+        <v>11</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
       <c r="F5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
+        <v>52</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
+        <v>15</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
+        <v>12</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+    </row>
+    <row r="8" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+    </row>
+    <row r="9" spans="1:10" ht="180.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-    </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-    </row>
-    <row r="9" spans="1:10" ht="180.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
       <c r="F10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
+        <v>19</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="46"/>
+        <v>16</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="47"/>
       <c r="F11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="46"/>
+        <v>17</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="47"/>
     </row>
     <row r="12" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="8.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1785,75 +1785,75 @@
       <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36" t="s">
+      <c r="H15" s="49"/>
+      <c r="I15" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="50"/>
+    </row>
+    <row r="16" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="25"/>
+    </row>
+    <row r="18" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="36"/>
-      <c r="G15" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="42"/>
-    </row>
-    <row r="16" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="25"/>
-      <c r="I17" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="25"/>
-    </row>
-    <row r="18" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48" t="s">
-        <v>26</v>
-      </c>
       <c r="B18" s="19"/>
-      <c r="C18" s="50"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="20"/>
-      <c r="E18" s="53"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="55"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="52"/>
+      <c r="I18" s="40"/>
       <c r="J18" s="21"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1878,17 +1878,17 @@
       <c r="A22" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="36"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="51"/>
       <c r="G22" s="26" t="s">
         <v>6</v>
       </c>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="17"/>
@@ -1918,35 +1918,35 @@
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="25"/>
       <c r="D24" s="31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F24" s="25"/>
       <c r="G24" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" s="34" t="s">
         <v>48</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="34" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="21"/>
@@ -1961,12 +1961,6 @@
     <row r="26" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A8:J8"/>
@@ -1980,6 +1974,12 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="G7:J7"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
